--- a/public/downloads/TangRevamped2024.xlsx
+++ b/public/downloads/TangRevamped2024.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="57">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>OH</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>H</t>
+  </si>
+  <si>
+    <t>OH</t>
   </si>
   <si>
     <t>COOH</t>
@@ -665,10 +688,10 @@
         <v>30</v>
       </c>
       <c r="N3" s="5">
-        <v>165.1036455631256</v>
+        <v>165103.6455631256</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03138255950639149</v>
+        <v>31.38255950639149</v>
       </c>
       <c r="P3" s="5">
         <v>5261</v>
@@ -715,10 +738,10 @@
         <v>30</v>
       </c>
       <c r="N4" s="5">
-        <v>158.0187437534332</v>
+        <v>158018.7437534332</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04942719541865287</v>
+        <v>49.42719541865287</v>
       </c>
       <c r="P4" s="5">
         <v>3197</v>
@@ -765,10 +788,10 @@
         <v>30</v>
       </c>
       <c r="N5" s="5">
-        <v>329.7236452102661</v>
+        <v>329723.6452102661</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1421835468780794</v>
+        <v>142.1835468780794</v>
       </c>
       <c r="P5" s="5">
         <v>2319</v>
@@ -815,10 +838,10 @@
         <v>30</v>
       </c>
       <c r="N6" s="5">
-        <v>200.0263392925262</v>
+        <v>200026.3392925262</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08548134157800266</v>
+        <v>85.48134157800266</v>
       </c>
       <c r="P6" s="5">
         <v>2340</v>
@@ -865,10 +888,10 @@
         <v>30</v>
       </c>
       <c r="N7" s="5">
-        <v>543.5290126800537</v>
+        <v>543529.0126800537</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1580485643152235</v>
+        <v>158.0485643152235</v>
       </c>
       <c r="P7" s="5">
         <v>3439</v>
@@ -915,10 +938,10 @@
         <v>30</v>
       </c>
       <c r="N8" s="5">
-        <v>100.2537860870361</v>
+        <v>100253.7860870361</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01328216561831427</v>
+        <v>13.28216561831427</v>
       </c>
       <c r="P8" s="5">
         <v>7548</v>
@@ -965,10 +988,10 @@
         <v>30</v>
       </c>
       <c r="N9" s="5">
-        <v>79.49190473556519</v>
+        <v>79491.90473556519</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02972771306490845</v>
+        <v>29.72771306490845</v>
       </c>
       <c r="P9" s="5">
         <v>2674</v>
@@ -1015,10 +1038,10 @@
         <v>30</v>
       </c>
       <c r="N10" s="5">
-        <v>214.9673616886139</v>
+        <v>214967.3616886139</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08115038191340652</v>
+        <v>81.15038191340652</v>
       </c>
       <c r="P10" s="5">
         <v>2649</v>
@@ -1065,10 +1088,10 @@
         <v>30</v>
       </c>
       <c r="N11" s="5">
-        <v>249.0774519443512</v>
+        <v>249077.4519443512</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04016082746603535</v>
+        <v>40.16082746603534</v>
       </c>
       <c r="P11" s="5">
         <v>6202</v>
@@ -1115,10 +1138,10 @@
         <v>30</v>
       </c>
       <c r="N12" s="5">
-        <v>52.41141080856323</v>
+        <v>52411.41080856323</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01810411426893376</v>
+        <v>18.10411426893376</v>
       </c>
       <c r="P12" s="5">
         <v>2895</v>
@@ -1165,10 +1188,10 @@
         <v>30</v>
       </c>
       <c r="N13" s="5">
-        <v>519.7505462169647</v>
+        <v>519750.5462169647</v>
       </c>
       <c r="O13" s="4">
-        <v>0.0825393911730927</v>
+        <v>82.5393911730927</v>
       </c>
       <c r="P13" s="5">
         <v>6297</v>
@@ -1215,10 +1238,10 @@
         <v>30</v>
       </c>
       <c r="N14" s="5">
-        <v>323.0840408802032</v>
+        <v>323084.0408802032</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2171263715592764</v>
+        <v>217.1263715592764</v>
       </c>
       <c r="P14" s="5">
         <v>1488</v>
@@ -1265,10 +1288,10 @@
         <v>30</v>
       </c>
       <c r="N15" s="5">
-        <v>501.998631477356</v>
+        <v>501998.631477356</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2159133898827338</v>
+        <v>215.9133898827338</v>
       </c>
       <c r="P15" s="5">
         <v>2325</v>
@@ -1315,10 +1338,10 @@
         <v>30</v>
       </c>
       <c r="N16" s="5">
-        <v>160.4258019924164</v>
+        <v>160425.8019924164</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1004544783922457</v>
+        <v>100.4544783922457</v>
       </c>
       <c r="P16" s="5">
         <v>1597</v>
@@ -1365,10 +1388,10 @@
         <v>30</v>
       </c>
       <c r="N17" s="5">
-        <v>287.7600383758545</v>
+        <v>287760.0383758545</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09754577572062864</v>
+        <v>97.54577572062864</v>
       </c>
       <c r="P17" s="5">
         <v>2950</v>
@@ -1396,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1407,9 +1430,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1443,8 +1472,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1466,25 +1503,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.09474687641576342</v>
+        <v>0.2630969506964362</v>
       </c>
       <c r="C3" s="4">
-        <v>0.09474687641576342</v>
+        <v>0.2630969506964362</v>
       </c>
       <c r="D3" s="4">
-        <v>0.09763702657301433</v>
+        <v>0.2911933578023435</v>
       </c>
       <c r="E3" s="4">
-        <v>78.79406307977737</v>
+        <v>84.97217068645639</v>
       </c>
       <c r="F3" s="4">
-        <v>88.00488102501528</v>
+        <v>92.47406955460649</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
@@ -1507,66 +1562,102 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2630969506964362</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04956106100799347</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04956106100799347</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1947706202817204</v>
+        <v>1.178183650519801</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1947706202817204</v>
+        <v>0.07295875792361922</v>
       </c>
       <c r="D4" s="4">
-        <v>0.224334354217464</v>
+        <v>2.361383600534388</v>
       </c>
       <c r="E4" s="4">
-        <v>79.72479901051331</v>
+        <v>77.35621521335774</v>
       </c>
       <c r="F4" s="4">
-        <v>90.03660768761441</v>
+        <v>82.29713239780185</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.03685095976073348</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.185084260133155</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07320373417088959</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2544506923824192</v>
+        <v>0.4846362023360267</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3268308555139399</v>
+        <v>0.5239713411961313</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2736548534713172</v>
+        <v>0.3842645478425801</v>
       </c>
       <c r="E5" s="4">
-        <v>55.76530612244898</v>
+        <v>57.85714285714285</v>
       </c>
       <c r="F5" s="4">
-        <v>63.55704697986577</v>
+        <v>64.07718120805369</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -1589,25 +1680,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4846362023360267</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5239713411961313</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3143918834546486</v>
+        <v>0.7121184591596581</v>
       </c>
       <c r="C6" s="4">
-        <v>0.3143918834546486</v>
+        <v>0.7121184591596581</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3779621199941552</v>
+        <v>0.7305399007501947</v>
       </c>
       <c r="E6" s="4">
-        <v>71.37755102040816</v>
+        <v>76.63265306122449</v>
       </c>
       <c r="F6" s="4">
-        <v>84.44630872483222</v>
+        <v>86.45973154362416</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -1630,25 +1737,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.7121184591596581</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.7121184591596581</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1123931277033456</v>
+        <v>0.4725309074808273</v>
       </c>
       <c r="C7" s="4">
-        <v>0.0451925030850866</v>
+        <v>0.3612830476727105</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1378065039790819</v>
+        <v>0.4964546904375169</v>
       </c>
       <c r="E7" s="4">
-        <v>62.5</v>
+        <v>70.25510204081633</v>
       </c>
       <c r="F7" s="4">
-        <v>65.15100671140939</v>
+        <v>69.39597315436242</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -1671,9 +1794,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.4725309074808273</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.3612830476727105</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1684,6 +1823,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1691,7 +1831,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1702,9 +1842,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1738,8 +1884,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1761,40 +1915,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.938481749401531</v>
+        <v>0.3408459350721387</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1212560072175014</v>
+        <v>0.3408459350721387</v>
       </c>
       <c r="D3" s="4">
-        <v>7.827139020900424</v>
+        <v>0.3296751842231474</v>
       </c>
       <c r="E3" s="4">
-        <v>74.36920222634507</v>
+        <v>85.00927643784787</v>
       </c>
       <c r="F3" s="4">
-        <v>80.44234289200614</v>
+        <v>90.9945088468578</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -1802,37 +1974,55 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3367356036525797</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1489709036516517</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1489709036516517</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4590393279415201</v>
+        <v>0.9663111447142992</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4590393279415201</v>
+        <v>0.3477650675695259</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4825976411378757</v>
+        <v>1.189996170883123</v>
       </c>
       <c r="E4" s="4">
-        <v>83.44155844155843</v>
+        <v>80.10204081632651</v>
       </c>
       <c r="F4" s="4">
-        <v>91.58633312995731</v>
+        <v>79.53325198291468</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -1841,27 +2031,45 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.6712546979267953</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8079239475450639</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3817031831843755</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1171750159592193</v>
+        <v>0.7167039780288178</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1171750159592193</v>
+        <v>0.7167039780288178</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1205829185273615</v>
+        <v>0.6545287041335541</v>
       </c>
       <c r="E5" s="4">
-        <v>72.67006802721093</v>
+        <v>74.28571428571429</v>
       </c>
       <c r="F5" s="4">
-        <v>80.03076062639683</v>
+        <v>73.33892617449665</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -1884,25 +2092,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7167039780288178</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7167039780288178</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3510054910584586</v>
+        <v>0.7988437974854605</v>
       </c>
       <c r="C6" s="4">
-        <v>0.3510054910584586</v>
+        <v>0.7988437974854605</v>
       </c>
       <c r="D6" s="4">
-        <v>0.375852521698107</v>
+        <v>0.7489175165101187</v>
       </c>
       <c r="E6" s="4">
-        <v>75.61224489795919</v>
+        <v>79.59183673469387</v>
       </c>
       <c r="F6" s="4">
-        <v>85.55369127516778</v>
+        <v>84.51342281879195</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -1925,25 +2149,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.7988437974854605</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.7988437974854605</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1056912819549325</v>
+        <v>0.2209902471440728</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1056912819549325</v>
+        <v>0.2209902471440728</v>
       </c>
       <c r="D7" s="4">
-        <v>0.123449630154937</v>
+        <v>0.2239735788243706</v>
       </c>
       <c r="E7" s="4">
-        <v>75.81632653061224</v>
+        <v>77.94217687074831</v>
       </c>
       <c r="F7" s="4">
-        <v>86.24161073825503</v>
+        <v>83.33892617449663</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -1966,9 +2206,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2209902471440728</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2209902471440728</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1979,6 +2235,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1986,7 +2243,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1997,9 +2254,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2033,8 +2296,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2056,34 +2327,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9583988436759021</v>
+        <v>0.1947706202817204</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1912091985036568</v>
+        <v>0.1947706202817204</v>
       </c>
       <c r="D3" s="4">
-        <v>2.687813133416388</v>
+        <v>0.224334354217464</v>
       </c>
       <c r="E3" s="4">
-        <v>73.57452071737757</v>
+        <v>79.72479901051331</v>
       </c>
       <c r="F3" s="4">
-        <v>76.63616026032122</v>
+        <v>90.03660768761441</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2097,25 +2386,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1328294490638013</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1321655612462193</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1321655612462193</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3133950782890183</v>
+        <v>0.09474687641576342</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3133950782890183</v>
+        <v>0.09474687641576342</v>
       </c>
       <c r="D4" s="4">
-        <v>0.341992885042683</v>
+        <v>0.09763702657301433</v>
       </c>
       <c r="E4" s="4">
-        <v>79.53617810760666</v>
+        <v>78.79406307977737</v>
       </c>
       <c r="F4" s="4">
-        <v>90.33658735001016</v>
+        <v>88.00488102501528</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
@@ -2138,34 +2445,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.02331169193204843</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09686612113685872</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09686612113685872</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2687564758925873</v>
+        <v>0.2544506923824192</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2687564758925873</v>
+        <v>0.3268308555139399</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3391214279799897</v>
+        <v>0.2736548534713172</v>
       </c>
       <c r="E5" s="4">
-        <v>67.35544217687074</v>
+        <v>55.76530612244898</v>
       </c>
       <c r="F5" s="4">
-        <v>81.76454138702461</v>
+        <v>63.55704697986577</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2179,25 +2504,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2544506923824192</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3268308555139399</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.289485391418566</v>
+        <v>0.3143918834546486</v>
       </c>
       <c r="C6" s="4">
-        <v>0.289485391418566</v>
+        <v>0.3143918834546486</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3491935098572867</v>
+        <v>0.3779621199941552</v>
       </c>
       <c r="E6" s="4">
-        <v>69.38775510204081</v>
+        <v>71.37755102040816</v>
       </c>
       <c r="F6" s="4">
-        <v>84.13870246085011</v>
+        <v>84.44630872483222</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -2220,25 +2561,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3143918834546486</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3143918834546486</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.02872425974783255</v>
+        <v>0.1123931277033456</v>
       </c>
       <c r="C7" s="4">
-        <v>0.01557657978264615</v>
+        <v>0.0451925030850866</v>
       </c>
       <c r="D7" s="4">
-        <v>0.04550630511221243</v>
+        <v>0.1378065039790819</v>
       </c>
       <c r="E7" s="4">
-        <v>60.40816326530612</v>
+        <v>62.5</v>
       </c>
       <c r="F7" s="4">
-        <v>65.06711409395973</v>
+        <v>65.15100671140939</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -2261,9 +2618,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1123931277033456</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.0451925030850866</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2274,6 +2647,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2281,7 +2655,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2292,9 +2666,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,8 +2708,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2351,81 +2739,117 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>2.257252628602477</v>
+        <v>0.4590393279415201</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1814090070656675</v>
+        <v>0.4590393279415201</v>
       </c>
       <c r="D3" s="4">
-        <v>4.604854844282685</v>
+        <v>0.4825976411378757</v>
       </c>
       <c r="E3" s="4">
-        <v>79.73098330241129</v>
+        <v>83.44155844155843</v>
       </c>
       <c r="F3" s="4">
-        <v>85.79316656497767</v>
+        <v>91.58633312995731</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4590393279415201</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1545577883514867</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1545577883514867</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3903254678632286</v>
+        <v>1.938481749401531</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3903254678632286</v>
+        <v>0.1212560072175014</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4128957527933711</v>
+        <v>7.827139020900424</v>
       </c>
       <c r="E4" s="4">
-        <v>85.38961038961038</v>
+        <v>74.36920222634507</v>
       </c>
       <c r="F4" s="4">
-        <v>92.96522269676635</v>
+        <v>80.44234289200614</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
         <v>0</v>
@@ -2433,25 +2857,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.0515675090221824</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.914277293186883</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1031322294045283</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6543632416396576</v>
+        <v>0.1171750159592193</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6543632416396576</v>
+        <v>0.1171750159592193</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7072025208144623</v>
+        <v>0.1205829185273615</v>
       </c>
       <c r="E5" s="4">
-        <v>76.32653061224489</v>
+        <v>72.67006802721093</v>
       </c>
       <c r="F5" s="4">
-        <v>85.88926174496645</v>
+        <v>80.03076062639683</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -2474,25 +2916,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1171750159592193</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1171750159592193</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.5883430803223746</v>
+        <v>0.3510054910584586</v>
       </c>
       <c r="C6" s="4">
-        <v>0.5883430803223746</v>
+        <v>0.3510054910584586</v>
       </c>
       <c r="D6" s="4">
-        <v>0.6418113077088492</v>
+        <v>0.375852521698107</v>
       </c>
       <c r="E6" s="4">
-        <v>77.44897959183673</v>
+        <v>75.61224489795919</v>
       </c>
       <c r="F6" s="4">
-        <v>87.88590604026845</v>
+        <v>85.55369127516778</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -2515,34 +2973,50 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3510054910584586</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3510054910584586</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.7094493574040825</v>
+        <v>0.1056912819549325</v>
       </c>
       <c r="C7" s="4">
-        <v>0.5836622502538376</v>
+        <v>0.1056912819549325</v>
       </c>
       <c r="D7" s="4">
-        <v>0.7256539529698784</v>
+        <v>0.123449630154937</v>
       </c>
       <c r="E7" s="4">
-        <v>68.57142857142857</v>
+        <v>75.81632653061224</v>
       </c>
       <c r="F7" s="4">
-        <v>67.34899328859061</v>
+        <v>86.24161073825503</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
@@ -2556,9 +3030,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1056912819549325</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1056912819549325</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2569,6 +3059,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2576,7 +3067,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2587,9 +3078,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2623,8 +3120,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2646,25 +3151,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1331922918937261</v>
+        <v>0.3133950782890183</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1331922918937261</v>
+        <v>0.3133950782890183</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1269994830922498</v>
+        <v>0.341992885042683</v>
       </c>
       <c r="E3" s="4">
-        <v>92.82931354359926</v>
+        <v>79.53617810760666</v>
       </c>
       <c r="F3" s="4">
-        <v>95.97010372178157</v>
+        <v>90.33658735001016</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
@@ -2687,34 +3210,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3099367051290756</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1067734050977213</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1067734050977213</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.07946144474242735</v>
+        <v>0.9583988436759021</v>
       </c>
       <c r="C4" s="4">
-        <v>0.07946144474242735</v>
+        <v>0.1912091985036568</v>
       </c>
       <c r="D4" s="4">
-        <v>0.09508008594440556</v>
+        <v>2.687813133416388</v>
       </c>
       <c r="E4" s="4">
-        <v>93.32096474953616</v>
+        <v>73.57452071737757</v>
       </c>
       <c r="F4" s="4">
-        <v>96.67480170835874</v>
+        <v>76.63616026032122</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2728,34 +3269,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1360862234182605</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9832073802141085</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.204527039275149</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.07321750250774572</v>
+        <v>0.2687564758925873</v>
       </c>
       <c r="C5" s="4">
-        <v>0.07321666804274063</v>
+        <v>0.2687564758925873</v>
       </c>
       <c r="D5" s="4">
-        <v>0.07570110884626446</v>
+        <v>0.3391214279799897</v>
       </c>
       <c r="E5" s="4">
-        <v>83.31632653061224</v>
+        <v>67.35544217687074</v>
       </c>
       <c r="F5" s="4">
-        <v>75.08389261744966</v>
+        <v>81.76454138702461</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2769,25 +3328,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2687564758925873</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2687564758925873</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1396111810609213</v>
+        <v>0.289485391418566</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1396111810609213</v>
+        <v>0.289485391418566</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1619351470872274</v>
+        <v>0.3491935098572867</v>
       </c>
       <c r="E6" s="4">
-        <v>93.57142857142857</v>
+        <v>69.38775510204081</v>
       </c>
       <c r="F6" s="4">
-        <v>96.10738255033557</v>
+        <v>84.13870246085011</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -2810,25 +3385,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.289485391418566</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.289485391418566</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.03462514082639245</v>
+        <v>0.02872425974783255</v>
       </c>
       <c r="C7" s="4">
-        <v>0.03283383586676791</v>
+        <v>0.01557657978264615</v>
       </c>
       <c r="D7" s="4">
-        <v>0.05676745711389941</v>
+        <v>0.04550630511221243</v>
       </c>
       <c r="E7" s="4">
-        <v>80.15306122448979</v>
+        <v>60.40816326530612</v>
       </c>
       <c r="F7" s="4">
-        <v>71.69463087248322</v>
+        <v>65.06711409395973</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -2851,9 +3442,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.02872425974783255</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.01557657978264615</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2864,6 +3471,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2871,7 +3479,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2882,9 +3490,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2918,8 +3532,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2941,25 +3563,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4093504041054265</v>
+        <v>0.3903254678632286</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4093504041054265</v>
+        <v>0.3903254678632286</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4337375361431988</v>
+        <v>0.4128957527933711</v>
       </c>
       <c r="E3" s="4">
-        <v>79.48051948051948</v>
+        <v>85.38961038961038</v>
       </c>
       <c r="F3" s="4">
-        <v>87.65710799267831</v>
+        <v>92.96522269676635</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
@@ -2982,66 +3622,102 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3903254678632286</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07638311281833703</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07638311281833703</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3985255606123908</v>
+        <v>2.257252628602477</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3985255606123908</v>
+        <v>0.1814090070656675</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4463696996248168</v>
+        <v>4.604854844282685</v>
       </c>
       <c r="E4" s="4">
-        <v>80.25974025974025</v>
+        <v>79.73098330241129</v>
       </c>
       <c r="F4" s="4">
-        <v>90.62843197071382</v>
+        <v>85.79316656497767</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1814090070656675</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.206503459821265</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07906913254070484</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.14790552541306</v>
+        <v>0.6543632416396576</v>
       </c>
       <c r="C5" s="4">
-        <v>1.14790552541306</v>
+        <v>0.6543632416396576</v>
       </c>
       <c r="D5" s="4">
-        <v>1.229544964280651</v>
+        <v>0.7072025208144623</v>
       </c>
       <c r="E5" s="4">
-        <v>68.5204081632653</v>
+        <v>76.32653061224489</v>
       </c>
       <c r="F5" s="4">
-        <v>83.02013422818791</v>
+        <v>85.88926174496645</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -3064,25 +3740,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6543632416396576</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6543632416396576</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.216814693252658</v>
+        <v>0.5883430803223746</v>
       </c>
       <c r="C6" s="4">
-        <v>1.216814693252658</v>
+        <v>0.5883430803223746</v>
       </c>
       <c r="D6" s="4">
-        <v>1.307691585461718</v>
+        <v>0.6418113077088492</v>
       </c>
       <c r="E6" s="4">
-        <v>69.94897959183673</v>
+        <v>77.44897959183673</v>
       </c>
       <c r="F6" s="4">
-        <v>84.59731543624162</v>
+        <v>87.88590604026845</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -3105,25 +3797,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5883430803223746</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.5883430803223746</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>1.284259206666327</v>
+        <v>0.7094493574040825</v>
       </c>
       <c r="C7" s="4">
-        <v>1.181356468412567</v>
+        <v>0.5836622502538376</v>
       </c>
       <c r="D7" s="4">
-        <v>1.296454838527985</v>
+        <v>0.7256539529698784</v>
       </c>
       <c r="E7" s="4">
-        <v>61.05442176870748</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="F7" s="4">
-        <v>64.19463087248322</v>
+        <v>67.34899328859061</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -3146,9 +3854,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.7094493574040825</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.5836622502538376</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3159,6 +3883,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3166,7 +3891,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3177,9 +3902,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3213,8 +3944,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3236,25 +3975,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1634188395033957</v>
+        <v>0.07946144474242735</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1634188395033957</v>
+        <v>0.07946144474242735</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1551929392976994</v>
+        <v>0.09508008594440556</v>
       </c>
       <c r="E3" s="4">
-        <v>92.35621521335806</v>
+        <v>93.32096474953616</v>
       </c>
       <c r="F3" s="4">
-        <v>95.4484441732763</v>
+        <v>96.67480170835874</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
@@ -3277,25 +4034,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.07754083942861133</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0456201060807837</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0456201060807837</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.08575608266090223</v>
+        <v>0.1331922918937261</v>
       </c>
       <c r="C4" s="4">
-        <v>0.08575608266090223</v>
+        <v>0.1331922918937261</v>
       </c>
       <c r="D4" s="4">
-        <v>0.100884000177097</v>
+        <v>0.1269994830922498</v>
       </c>
       <c r="E4" s="4">
-        <v>92.76437847866418</v>
+        <v>92.82931354359926</v>
       </c>
       <c r="F4" s="4">
-        <v>96.2660158633313</v>
+        <v>95.97010372178157</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
@@ -3318,25 +4093,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1331922918937261</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.03979669743162893</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03979669743162893</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.04253598571082451</v>
+        <v>0.07321750250774572</v>
       </c>
       <c r="C5" s="4">
-        <v>0.04122235504110794</v>
+        <v>0.07321666804274063</v>
       </c>
       <c r="D5" s="4">
-        <v>0.07931246131918401</v>
+        <v>0.07570110884626446</v>
       </c>
       <c r="E5" s="4">
-        <v>80.64625850340137</v>
+        <v>83.31632653061224</v>
       </c>
       <c r="F5" s="4">
-        <v>71.76174496644295</v>
+        <v>75.08389261744966</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -3359,25 +4152,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07321750250774572</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07321666804274063</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.09822404031002918</v>
+        <v>0.1396111810609213</v>
       </c>
       <c r="C6" s="4">
-        <v>0.09822404031002918</v>
+        <v>0.1396111810609213</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1260243320866863</v>
+        <v>0.1619351470872274</v>
       </c>
       <c r="E6" s="4">
-        <v>93.72448979591837</v>
+        <v>93.57142857142857</v>
       </c>
       <c r="F6" s="4">
-        <v>96.04026845637584</v>
+        <v>96.10738255033557</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -3400,25 +4209,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1396111810609213</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1396111810609213</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.08147569833818125</v>
+        <v>0.03462514082639245</v>
       </c>
       <c r="C7" s="4">
-        <v>0.146489909675438</v>
+        <v>0.03283383586676791</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1323361182075757</v>
+        <v>0.05676745711389941</v>
       </c>
       <c r="E7" s="4">
-        <v>81.27551020408163</v>
+        <v>80.15306122448979</v>
       </c>
       <c r="F7" s="4">
-        <v>71.89597315436242</v>
+        <v>71.69463087248322</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -3441,9 +4266,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.03462514082639245</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.03283383586676791</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3454,6 +4295,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3461,7 +4303,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3472,9 +4314,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3508,8 +4356,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3531,66 +4387,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6625886807818072</v>
+        <v>0.3985255606123908</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2052005719011029</v>
+        <v>0.3985255606123908</v>
       </c>
       <c r="D3" s="4">
-        <v>3.172236082678198</v>
+        <v>0.4463696996248168</v>
       </c>
       <c r="E3" s="4">
-        <v>74.39393939393906</v>
+        <v>80.25974025974025</v>
       </c>
       <c r="F3" s="4">
-        <v>79.84950172869463</v>
+        <v>90.62843197071382</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3985255606123908</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05594176796816253</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05594176796816253</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2786712350144505</v>
+        <v>0.4093504041054265</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2786712350144505</v>
+        <v>0.4093504041054265</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3149943515987171</v>
+        <v>0.4337375361431988</v>
       </c>
       <c r="E4" s="4">
-        <v>80.85343228200369</v>
+        <v>79.48051948051948</v>
       </c>
       <c r="F4" s="4">
-        <v>90.57352043929218</v>
+        <v>87.65710799267831</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
@@ -3613,34 +4505,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4093504041054265</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1117807888930527</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1117807888930527</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.114660148170495</v>
+        <v>1.14790552541306</v>
       </c>
       <c r="C5" s="4">
-        <v>1.167249113645084</v>
+        <v>1.14790552541306</v>
       </c>
       <c r="D5" s="4">
-        <v>1.147599455562139</v>
+        <v>1.229544964280651</v>
       </c>
       <c r="E5" s="4">
-        <v>57.09183673469388</v>
+        <v>68.5204081632653</v>
       </c>
       <c r="F5" s="4">
-        <v>63.65771812080537</v>
+        <v>83.02013422818791</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -3654,25 +4564,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.14790552541306</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.14790552541306</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.9878975713654512</v>
+        <v>1.216814693252658</v>
       </c>
       <c r="C6" s="4">
-        <v>0.9878975713654512</v>
+        <v>1.216814693252658</v>
       </c>
       <c r="D6" s="4">
-        <v>1.09265476111613</v>
+        <v>1.307691585461718</v>
       </c>
       <c r="E6" s="4">
-        <v>71.93877551020408</v>
+        <v>69.94897959183673</v>
       </c>
       <c r="F6" s="4">
-        <v>85.58724832214764</v>
+        <v>84.59731543624162</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -3695,25 +4621,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.216814693252658</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>1.216814693252658</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.748259163512536</v>
+        <v>1.284259206666327</v>
       </c>
       <c r="C7" s="4">
-        <v>0.5993468548985632</v>
+        <v>1.181356468412567</v>
       </c>
       <c r="D7" s="4">
-        <v>0.7862846619027337</v>
+        <v>1.296454838527985</v>
       </c>
       <c r="E7" s="4">
-        <v>65.45918367346938</v>
+        <v>61.05442176870748</v>
       </c>
       <c r="F7" s="4">
-        <v>68.69686800894854</v>
+        <v>64.19463087248322</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -3736,9 +4678,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.284259206666327</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.181356468412567</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3749,12 +4707,1694 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.08575608266090223</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.08575608266090223</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.100884000177097</v>
+      </c>
+      <c r="E3" s="4">
+        <v>92.76437847866418</v>
+      </c>
+      <c r="F3" s="4">
+        <v>96.2660158633313</v>
+      </c>
+      <c r="G3" s="5">
+        <v>11</v>
+      </c>
+      <c r="H3" s="5">
+        <v>11</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.08302931368929091</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04866441664128376</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04866441664128376</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1634188395033957</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1634188395033957</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1551929392976994</v>
+      </c>
+      <c r="E4" s="4">
+        <v>92.35621521335806</v>
+      </c>
+      <c r="F4" s="4">
+        <v>95.4484441732763</v>
+      </c>
+      <c r="G4" s="5">
+        <v>11</v>
+      </c>
+      <c r="H4" s="5">
+        <v>11</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1634188395033957</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.03562205657194562</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03562205657194562</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.04253598571082451</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.04122235504110794</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.07931246131918401</v>
+      </c>
+      <c r="E5" s="4">
+        <v>80.64625850340137</v>
+      </c>
+      <c r="F5" s="4">
+        <v>71.76174496644295</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.04253598571082451</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04122235504110794</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.09822404031002918</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.09822404031002918</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.1260243320866863</v>
+      </c>
+      <c r="E6" s="4">
+        <v>93.72448979591837</v>
+      </c>
+      <c r="F6" s="4">
+        <v>96.04026845637584</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.09822404031002918</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.09822404031002918</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.08147569833818125</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.146489909675438</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.1323361182075757</v>
+      </c>
+      <c r="E7" s="4">
+        <v>81.27551020408163</v>
+      </c>
+      <c r="F7" s="4">
+        <v>71.89597315436242</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.08147569833818125</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.146489909675438</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2786712350144505</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2786712350144505</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3149943515987171</v>
+      </c>
+      <c r="E3" s="4">
+        <v>80.85343228200369</v>
+      </c>
+      <c r="F3" s="4">
+        <v>90.57352043929218</v>
+      </c>
+      <c r="G3" s="5">
+        <v>11</v>
+      </c>
+      <c r="H3" s="5">
+        <v>11</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2786712350144505</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05419965369261871</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05419965369261871</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.6625886807818072</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2052005719011029</v>
+      </c>
+      <c r="D4" s="4">
+        <v>3.172236082678198</v>
+      </c>
+      <c r="E4" s="4">
+        <v>74.39393939393906</v>
+      </c>
+      <c r="F4" s="4">
+        <v>79.84950172869463</v>
+      </c>
+      <c r="G4" s="5">
+        <v>11</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2052005719011029</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6396290586518693</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1315386844309336</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.114660148170495</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1.167249113645084</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.147599455562139</v>
+      </c>
+      <c r="E5" s="4">
+        <v>57.09183673469388</v>
+      </c>
+      <c r="F5" s="4">
+        <v>63.65771812080537</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.114660148170495</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.167249113645084</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.9878975713654512</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.9878975713654512</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1.09265476111613</v>
+      </c>
+      <c r="E6" s="4">
+        <v>71.93877551020408</v>
+      </c>
+      <c r="F6" s="4">
+        <v>85.58724832214764</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.9878975713654512</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.9878975713654512</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.748259163512536</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.5993468548985632</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.7862846619027337</v>
+      </c>
+      <c r="E7" s="4">
+        <v>65.45918367346938</v>
+      </c>
+      <c r="F7" s="4">
+        <v>68.69686800894854</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.748259163512536</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.5993468548985632</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="C3" s="3">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.6532059792653367</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2599220006475014</v>
+      </c>
+      <c r="J3" s="4">
+        <v>2.874906097190797</v>
+      </c>
+      <c r="K3" s="4">
+        <v>77.37641723356033</v>
+      </c>
+      <c r="L3" s="4">
+        <v>83.64802386278835</v>
+      </c>
+      <c r="M3" s="5">
+        <v>30</v>
+      </c>
+      <c r="N3" s="5">
+        <v>165103.6455631256</v>
+      </c>
+      <c r="O3" s="4">
+        <v>31.38255950639149</v>
+      </c>
+      <c r="P3" s="5">
+        <v>5261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="C4" s="3">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.266154781037003</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2179814945462883</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2742873336770451</v>
+      </c>
+      <c r="K4" s="4">
+        <v>70.41609977324256</v>
+      </c>
+      <c r="L4" s="4">
+        <v>77.22147651006647</v>
+      </c>
+      <c r="M4" s="5">
+        <v>30</v>
+      </c>
+      <c r="N4" s="5">
+        <v>158018.7437534332</v>
+      </c>
+      <c r="O4" s="4">
+        <v>49.42719541865287</v>
+      </c>
+      <c r="P4" s="5">
+        <v>3197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>90</v>
+      </c>
+      <c r="C5" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D5" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1.205755515766875</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.658061639306006</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.602590063902916</v>
+      </c>
+      <c r="K5" s="4">
+        <v>78.94897959183665</v>
+      </c>
+      <c r="L5" s="4">
+        <v>87.41722595078143</v>
+      </c>
+      <c r="M5" s="5">
+        <v>30</v>
+      </c>
+      <c r="N5" s="5">
+        <v>329723.6452102661</v>
+      </c>
+      <c r="O5" s="4">
+        <v>142.1835468780794</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>96.66666666666667</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4098728289733117</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3321806318348889</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.4403944912223696</v>
+      </c>
+      <c r="K6" s="4">
+        <v>81.014739229025</v>
+      </c>
+      <c r="L6" s="4">
+        <v>87.08090976882795</v>
+      </c>
+      <c r="M6" s="5">
+        <v>30</v>
+      </c>
+      <c r="N6" s="5">
+        <v>200026.3392925262</v>
+      </c>
+      <c r="O6" s="4">
+        <v>85.48134157800266</v>
+      </c>
+      <c r="P6" s="5">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>90</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.8583176326679273</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.08611096827320609</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1.914151321119695</v>
+      </c>
+      <c r="K7" s="4">
+        <v>80.54308390022695</v>
+      </c>
+      <c r="L7" s="4">
+        <v>86.83929903057567</v>
+      </c>
+      <c r="M7" s="5">
+        <v>30</v>
+      </c>
+      <c r="N7" s="5">
+        <v>543529.0126800537</v>
+      </c>
+      <c r="O7" s="4">
+        <v>158.0485643152235</v>
+      </c>
+      <c r="P7" s="5">
+        <v>3439</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C8" s="3">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.5962980691725904</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1614987170804089</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1.025615705787393</v>
+      </c>
+      <c r="K8" s="4">
+        <v>77.02721088435359</v>
+      </c>
+      <c r="L8" s="4">
+        <v>83.01677852349056</v>
+      </c>
+      <c r="M8" s="5">
+        <v>30</v>
+      </c>
+      <c r="N8" s="5">
+        <v>100253.7860870361</v>
+      </c>
+      <c r="O8" s="4">
+        <v>13.28216561831427</v>
+      </c>
+      <c r="P8" s="5">
+        <v>7548</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>90</v>
+      </c>
+      <c r="C9" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.5144109121512737</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3555107187784263</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.5653068064540883</v>
+      </c>
+      <c r="K9" s="4">
+        <v>80.9478458049887</v>
+      </c>
+      <c r="L9" s="4">
+        <v>83.49552572707067</v>
+      </c>
+      <c r="M9" s="5">
+        <v>30</v>
+      </c>
+      <c r="N9" s="5">
+        <v>79491.90473556519</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.72771306490845</v>
+      </c>
+      <c r="P9" s="5">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>90</v>
+      </c>
+      <c r="C10" s="3">
+        <v>10</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1463573766019841</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1424809810087452</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1609600690771466</v>
+      </c>
+      <c r="K10" s="4">
+        <v>74.48412698412719</v>
+      </c>
+      <c r="L10" s="4">
+        <v>83.72930648769575</v>
+      </c>
+      <c r="M10" s="5">
+        <v>30</v>
+      </c>
+      <c r="N10" s="5">
+        <v>214967.3616886139</v>
+      </c>
+      <c r="O10" s="4">
+        <v>81.15038191340652</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="E11" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.8046426502261911</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1432292623703846</v>
+      </c>
+      <c r="J11" s="4">
+        <v>2.962760703093565</v>
+      </c>
+      <c r="K11" s="4">
+        <v>77.64852607709763</v>
+      </c>
+      <c r="L11" s="4">
+        <v>85.20096942580096</v>
+      </c>
+      <c r="M11" s="5">
+        <v>30</v>
+      </c>
+      <c r="N11" s="5">
+        <v>249077.4519443512</v>
+      </c>
+      <c r="O11" s="4">
+        <v>40.16082746603534</v>
+      </c>
+      <c r="P11" s="5">
+        <v>6202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="C12" s="3">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.4567077948111091</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1723191167871636</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1.103732132844364</v>
+      </c>
+      <c r="K12" s="4">
+        <v>73.77437641723354</v>
+      </c>
+      <c r="L12" s="4">
+        <v>82.07233407904607</v>
+      </c>
+      <c r="M12" s="5">
+        <v>30</v>
+      </c>
+      <c r="N12" s="5">
+        <v>52411.41080856323</v>
+      </c>
+      <c r="O12" s="4">
+        <v>18.10411426893376</v>
+      </c>
+      <c r="P12" s="5">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>90</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D13" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1.010826338034906</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2196162152342692</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1.890809465341965</v>
+      </c>
+      <c r="K13" s="4">
+        <v>80.45578231292534</v>
+      </c>
+      <c r="L13" s="4">
+        <v>87.34563758389436</v>
+      </c>
+      <c r="M13" s="5">
+        <v>30</v>
+      </c>
+      <c r="N13" s="5">
+        <v>519750.5462169647</v>
+      </c>
+      <c r="O13" s="4">
+        <v>82.5393911730927</v>
+      </c>
+      <c r="P13" s="5">
+        <v>6297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>90</v>
+      </c>
+      <c r="C14" s="3">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.05269758308140497</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.05178053232261595</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.05742654122106462</v>
+      </c>
+      <c r="K14" s="4">
+        <v>90.94557823129233</v>
+      </c>
+      <c r="L14" s="4">
+        <v>91.8344519015659</v>
+      </c>
+      <c r="M14" s="5">
+        <v>30</v>
+      </c>
+      <c r="N14" s="5">
+        <v>323084.0408802032</v>
+      </c>
+      <c r="O14" s="4">
+        <v>217.1263715592764</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>96.66666666666667</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.381290600898786</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.3466053821394308</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.4101185145143642</v>
+      </c>
+      <c r="K15" s="4">
+        <v>76.44104308390017</v>
+      </c>
+      <c r="L15" s="4">
+        <v>86.3601789709157</v>
+      </c>
+      <c r="M15" s="5">
+        <v>30</v>
+      </c>
+      <c r="N15" s="5">
+        <v>501998.631477356</v>
+      </c>
+      <c r="O15" s="4">
+        <v>215.9133898827338</v>
+      </c>
+      <c r="P15" s="5">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>90</v>
+      </c>
+      <c r="C16" s="3">
+        <v>10</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.04855648751617473</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.05009384836011983</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.06132908069100877</v>
+      </c>
+      <c r="K16" s="4">
+        <v>90.297052154195</v>
+      </c>
+      <c r="L16" s="4">
+        <v>91.05928411633103</v>
+      </c>
+      <c r="M16" s="5">
+        <v>30</v>
+      </c>
+      <c r="N16" s="5">
+        <v>160425.8019924164</v>
+      </c>
+      <c r="O16" s="4">
+        <v>100.4544783922457</v>
+      </c>
+      <c r="P16" s="5">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C17" s="3">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.5187689966075774</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2675873830166737</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1.452278902391568</v>
+      </c>
+      <c r="K17" s="4">
+        <v>73.69614512471648</v>
+      </c>
+      <c r="L17" s="4">
+        <v>81.26174496644283</v>
+      </c>
+      <c r="M17" s="5">
+        <v>30</v>
+      </c>
+      <c r="N17" s="5">
+        <v>287760.0383758545</v>
+      </c>
+      <c r="O17" s="4">
+        <v>97.54577572062864</v>
+      </c>
+      <c r="P17" s="5">
+        <v>2950</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3868,10 +6508,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -4047,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -4223,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -4311,7 +6951,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -4509,9 +7149,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>26</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>23</v>
+      </c>
+      <c r="C4" s="5">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>27</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>29</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>27</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>28</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>26</v>
+      </c>
+      <c r="C12" s="5">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>27</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>27</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>29</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>27</v>
+      </c>
+      <c r="C16" s="5">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4522,9 +7917,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4558,8 +7959,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4581,40 +7990,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.186414006958247</v>
+        <v>0.3488383592858471</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1736042462576329</v>
+        <v>0.3488383592858471</v>
       </c>
       <c r="D3" s="4">
-        <v>7.24930150445851</v>
+        <v>0.3679914340705595</v>
       </c>
       <c r="E3" s="4">
-        <v>76.21830550401975</v>
+        <v>84.02597402597401</v>
       </c>
       <c r="F3" s="4">
-        <v>82.66117551352281</v>
+        <v>91.83343502135446</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -4622,40 +8049,58 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3488383592858471</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09805841744811974</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09805841744811974</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3488383592858471</v>
+        <v>1.186414006958247</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3488383592858471</v>
+        <v>0.1736042462576329</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3679914340705595</v>
+        <v>7.24930150445851</v>
       </c>
       <c r="E4" s="4">
-        <v>84.02597402597401</v>
+        <v>76.21830550401975</v>
       </c>
       <c r="F4" s="4">
-        <v>91.83343502135446</v>
+        <v>82.66117551352281</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
         <v>0</v>
@@ -4663,10 +8108,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1554799685016203</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.116131417077144</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1222544071810891</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.7348557381301362</v>
@@ -4704,10 +8167,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7348557381301362</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.639185757307132</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>1.04959481600963</v>
@@ -4745,10 +8224,26 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.04959481600963</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>1.04959481600963</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>0.6007393068211968</v>
@@ -4786,9 +8281,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.6007393068211968</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.6007393068211968</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4799,14 +8310,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4817,9 +8329,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4853,8 +8371,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4876,25 +8402,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4307645145166713</v>
+        <v>0.3556310346509484</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4073913934531447</v>
+        <v>0.3453405355259747</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4111822862895761</v>
+        <v>0.3657926945852523</v>
       </c>
       <c r="E3" s="4">
-        <v>75.35250463821892</v>
+        <v>75.49783549783547</v>
       </c>
       <c r="F3" s="4">
-        <v>82.78116737848194</v>
+        <v>84.68375025421994</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
@@ -4917,25 +8461,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3453405355259747</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1549147202998773</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.159086643292394</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3556310346509484</v>
+        <v>0.4307645145166713</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3453405355259747</v>
+        <v>0.4073913934531447</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3657926945852523</v>
+        <v>0.4111822862895761</v>
       </c>
       <c r="E4" s="4">
-        <v>75.49783549783547</v>
+        <v>75.35250463821892</v>
       </c>
       <c r="F4" s="4">
-        <v>84.68375025421994</v>
+        <v>82.78116737848194</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
@@ -4958,17 +8520,33 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4073913934531447</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1765620915692786</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1685078675563272</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5731810001998383</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
         <v>0.5007394222884614</v>
       </c>
@@ -4999,10 +8577,24 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5731810001998383</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.7644843423768179</v>
@@ -5040,10 +8632,26 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.7644843423768179</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.7644843423768179</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>0.2583529074981925</v>
@@ -5081,9 +8689,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2583529074981925</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2086605813237838</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5094,14 +8718,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5112,9 +8737,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5148,8 +8779,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5171,37 +8810,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.880605037726623</v>
+        <v>0.2609036429616522</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2868342858138931</v>
+        <v>0.2609036429616522</v>
       </c>
       <c r="D3" s="4">
-        <v>2.919503042314649</v>
+        <v>0.299984305445171</v>
       </c>
       <c r="E3" s="4">
-        <v>80.98330241187386</v>
+        <v>83.40445269016696</v>
       </c>
       <c r="F3" s="4">
-        <v>88.95668090298953</v>
+        <v>91.58023184868823</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -5210,53 +8867,89 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2295051564198564</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1111106003615029</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1111106003615029</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2609036429616522</v>
+        <v>1.880605037726623</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2609036429616522</v>
+        <v>0.2868342858138931</v>
       </c>
       <c r="D4" s="4">
-        <v>0.299984305445171</v>
+        <v>2.919503042314649</v>
       </c>
       <c r="E4" s="4">
-        <v>83.40445269016696</v>
+        <v>80.98330241187386</v>
       </c>
       <c r="F4" s="4">
-        <v>91.58023184868823</v>
+        <v>88.95668090298953</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
       </c>
       <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.688313971091371</v>
+      </c>
+      <c r="O4" s="5">
         <v>11</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="P4" s="4">
+        <v>2.932727015593192</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.564772751419264</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3615627946674067</v>
@@ -5294,10 +8987,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3615627946674067</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3615627946674067</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.5011571461363928</v>
@@ -5335,10 +9044,26 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5011571461363928</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.5011571461363928</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>0.1209431132811005</v>
@@ -5376,9 +9101,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1209431132811005</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.01392742356983945</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5389,14 +9130,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5407,9 +9149,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5443,8 +9191,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5466,37 +9222,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4686057090290309</v>
+        <v>0.3600486058054561</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2169608036845602</v>
+        <v>0.3600486058054561</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5612279863969227</v>
+        <v>0.3809721986329929</v>
       </c>
       <c r="E3" s="4">
-        <v>82.72727272727272</v>
+        <v>84.23933209647494</v>
       </c>
       <c r="F3" s="4">
-        <v>88.59365466747998</v>
+        <v>90.54911531421595</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -5505,53 +9279,89 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3600486058054561</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1300122654042639</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1300122654042639</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3600486058054561</v>
+        <v>0.4686057090290309</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3600486058054561</v>
+        <v>0.2169608036845602</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3809721986329929</v>
+        <v>0.5612279863969227</v>
       </c>
       <c r="E4" s="4">
-        <v>84.23933209647494</v>
+        <v>82.72727272727272</v>
       </c>
       <c r="F4" s="4">
-        <v>90.54911531421595</v>
+        <v>88.59365466747998</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
       </c>
       <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.3221082164861648</v>
+      </c>
+      <c r="O4" s="5">
         <v>11</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="P4" s="4">
+        <v>0.5643922479704532</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3545368181687413</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5485034851699311</v>
@@ -5589,10 +9399,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5485034851699311</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5485034851699311</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.7165169084473746</v>
@@ -5630,10 +9456,26 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.7165169084473746</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.7165169084473746</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>0.5153437322514947</v>
@@ -5671,9 +9513,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.5153437322514947</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.5153437322514947</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5684,14 +9542,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5702,9 +9561,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5738,8 +9603,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5761,92 +9634,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>2.168986934496802</v>
+        <v>0.2179855733083969</v>
       </c>
       <c r="C3" s="4">
-        <v>0.07124598882971138</v>
+        <v>0.2179855733083969</v>
       </c>
       <c r="D3" s="4">
-        <v>4.98494009321869</v>
+        <v>0.2460813388557157</v>
       </c>
       <c r="E3" s="4">
-        <v>78.69820655534875</v>
+        <v>85.67717996289424</v>
       </c>
       <c r="F3" s="4">
-        <v>83.96379906446886</v>
+        <v>93.11470408785847</v>
       </c>
       <c r="G3" s="5">
         <v>11</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2179855733083969</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04919492506980367</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04919492506980367</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2179855733083969</v>
+        <v>2.168986934496802</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2179855733083969</v>
+        <v>0.07124598882971138</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2460813388557157</v>
+        <v>4.98494009321869</v>
       </c>
       <c r="E4" s="4">
-        <v>85.67717996289424</v>
+        <v>78.69820655534875</v>
       </c>
       <c r="F4" s="4">
-        <v>93.11470408785847</v>
+        <v>83.96379906446886</v>
       </c>
       <c r="G4" s="5">
         <v>11</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.001144310746086477</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.168674849747869</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07111884319125733</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1919022469191987</v>
@@ -5884,10 +9811,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1919022469191987</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1919022469191987</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.1831588113709586</v>
@@ -5925,10 +9868,26 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1831588113709586</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1831588113709586</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>0.1095174233123544</v>
@@ -5966,9 +9925,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1095174233123544</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.009855768468696624</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5979,596 +9954,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.178183650519801</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.07295875792361922</v>
-      </c>
-      <c r="D3" s="4">
-        <v>2.361383600534388</v>
-      </c>
-      <c r="E3" s="4">
-        <v>77.35621521335774</v>
-      </c>
-      <c r="F3" s="4">
-        <v>82.29713239780185</v>
-      </c>
-      <c r="G3" s="5">
-        <v>11</v>
-      </c>
-      <c r="H3" s="5">
-        <v>9</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2630969506964362</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2630969506964362</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2911933578023435</v>
-      </c>
-      <c r="E4" s="4">
-        <v>84.97217068645639</v>
-      </c>
-      <c r="F4" s="4">
-        <v>92.47406955460649</v>
-      </c>
-      <c r="G4" s="5">
-        <v>11</v>
-      </c>
-      <c r="H4" s="5">
-        <v>11</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4846362023360267</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.5239713411961313</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3842645478425801</v>
-      </c>
-      <c r="E5" s="4">
-        <v>57.85714285714285</v>
-      </c>
-      <c r="F5" s="4">
-        <v>64.07718120805369</v>
-      </c>
-      <c r="G5" s="5">
-        <v>4</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.7121184591596581</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.7121184591596581</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.7305399007501947</v>
-      </c>
-      <c r="E6" s="4">
-        <v>76.63265306122449</v>
-      </c>
-      <c r="F6" s="4">
-        <v>86.45973154362416</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.4725309074808273</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.3612830476727105</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.4964546904375169</v>
-      </c>
-      <c r="E7" s="4">
-        <v>70.25510204081633</v>
-      </c>
-      <c r="F7" s="4">
-        <v>69.39597315436242</v>
-      </c>
-      <c r="G7" s="5">
-        <v>2</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.9663111447142992</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3477650675695259</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.189996170883123</v>
-      </c>
-      <c r="E3" s="4">
-        <v>80.10204081632651</v>
-      </c>
-      <c r="F3" s="4">
-        <v>79.53325198291468</v>
-      </c>
-      <c r="G3" s="5">
-        <v>11</v>
-      </c>
-      <c r="H3" s="5">
-        <v>8</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3408459350721387</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3408459350721387</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3296751842231474</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.00927643784787</v>
-      </c>
-      <c r="F4" s="4">
-        <v>90.9945088468578</v>
-      </c>
-      <c r="G4" s="5">
-        <v>11</v>
-      </c>
-      <c r="H4" s="5">
-        <v>11</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7167039780288178</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7167039780288178</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6545287041335541</v>
-      </c>
-      <c r="E5" s="4">
-        <v>74.28571428571429</v>
-      </c>
-      <c r="F5" s="4">
-        <v>73.33892617449665</v>
-      </c>
-      <c r="G5" s="5">
-        <v>4</v>
-      </c>
-      <c r="H5" s="5">
-        <v>4</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.7988437974854605</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.7988437974854605</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.7489175165101187</v>
-      </c>
-      <c r="E6" s="4">
-        <v>79.59183673469387</v>
-      </c>
-      <c r="F6" s="4">
-        <v>84.51342281879195</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.2209902471440728</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.2209902471440728</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.2239735788243706</v>
-      </c>
-      <c r="E7" s="4">
-        <v>77.94217687074831</v>
-      </c>
-      <c r="F7" s="4">
-        <v>83.33892617449663</v>
-      </c>
-      <c r="G7" s="5">
-        <v>2</v>
-      </c>
-      <c r="H7" s="5">
-        <v>2</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/TangRevamped2024.xlsx
+++ b/public/downloads/TangRevamped2024.xlsx
@@ -1563,16 +1563,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2630969506964362</v>
+        <v>-0.2768612411381355</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04956106100799347</v>
+        <v>0.0483097618769299</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04956106100799347</v>
+        <v>0.0483097618769299</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -1622,16 +1622,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03685095976073348</v>
+        <v>-0.01732308676765015</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>1.185084260133155</v>
+        <v>1.179758476589587</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07320373417088959</v>
+        <v>0.07103397050499144</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3367356036525797</v>
+        <v>-0.332579818830709</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1489709036516517</v>
+        <v>0.1485931050314817</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1489709036516517</v>
+        <v>0.1485931050314817</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -2034,16 +2034,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6712546979267953</v>
+        <v>0.2824715527312947</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8079239475450639</v>
+        <v>0.7910016690019058</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3817031831843755</v>
+        <v>0.2126413707392203</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -2387,16 +2387,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1328294490638013</v>
+        <v>-0.1807894493627487</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1321655612462193</v>
+        <v>0.1262892253950069</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1321655612462193</v>
+        <v>0.1262892253950069</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.02331169193204843</v>
+        <v>0.0149299005095429</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09686612113685872</v>
+        <v>0.09338961273307769</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09686612113685872</v>
+        <v>0.09338961273307769</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -2799,16 +2799,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4590393279415201</v>
+        <v>-0.5224066224036505</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1545577883514867</v>
+        <v>0.1487971252185658</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1545577883514867</v>
+        <v>0.1487971252185658</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -2858,16 +2858,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0515675090221824</v>
+        <v>0.06542670674753026</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>1.914277293186883</v>
+        <v>1.910497511989061</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1031322294045283</v>
+        <v>0.1015923185461563</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -3211,16 +3211,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3099367051290756</v>
+        <v>-0.3034097525815014</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1067734050977213</v>
+        <v>0.1053667998424895</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1067734050977213</v>
+        <v>0.1053667998424895</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -3270,16 +3270,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1360862234182605</v>
+        <v>-0.04140743016614579</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9832073802141085</v>
+        <v>0.9617321624943791</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.204527039275149</v>
+        <v>0.1906165831082944</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -3623,16 +3623,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3903254678632286</v>
+        <v>-0.4380645161036227</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07638311281833703</v>
+        <v>0.06730409515809944</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07638311281833703</v>
+        <v>0.06730409515809944</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -3682,16 +3682,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1814090070656675</v>
+        <v>-0.1555101361082052</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>2.206503459821265</v>
+        <v>2.197881601729354</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07906913254070484</v>
+        <v>0.0742866106411384</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -4035,16 +4035,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07754083942861133</v>
+        <v>-0.08478520486823982</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0456201060807837</v>
+        <v>0.04386181524188518</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0456201060807837</v>
+        <v>0.04386181524188518</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -4094,16 +4094,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1331922918937261</v>
+        <v>0.1373571152253135</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.03979669743162893</v>
+        <v>0.03941807712875735</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03979669743162893</v>
+        <v>0.03941807712875735</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -4447,16 +4447,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3985255606123908</v>
+        <v>-0.4111573105219577</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05594176796816253</v>
+        <v>0.05479342706729282</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05594176796816253</v>
+        <v>0.05479342706729282</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -4506,16 +4506,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4093504041054265</v>
+        <v>-0.4035608204503554</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1117807888930527</v>
+        <v>0.1112544631062281</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1117807888930527</v>
+        <v>0.1112544631062281</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -4859,16 +4859,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08302931368929091</v>
+        <v>-0.09011307410037261</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04866441664128376</v>
+        <v>0.04802043842209452</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04866441664128376</v>
+        <v>0.04802043842209452</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -4918,16 +4918,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1634188395033957</v>
+        <v>0.1599428666741005</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.03562205657194562</v>
+        <v>0.0353060590420097</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03562205657194562</v>
+        <v>0.0353060590420097</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -5271,16 +5271,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2786712350144505</v>
+        <v>-0.2653028812346179</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05419965369261871</v>
+        <v>0.05298434880354302</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05419965369261871</v>
+        <v>0.05298434880354302</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -5330,16 +5330,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2052005719011029</v>
+        <v>-0.1763888597379228</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6396290586518693</v>
+        <v>0.6317713189710019</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1315386844309336</v>
+        <v>0.1283373830794691</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -5647,13 +5647,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.6532059792653367</v>
+        <v>0.6485700380292353</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2599220006475014</v>
+        <v>0.2561198864697452</v>
       </c>
       <c r="J3" s="4">
-        <v>2.874906097190797</v>
+        <v>2.870833700058817</v>
       </c>
       <c r="K3" s="4">
         <v>77.37641723356033</v>
@@ -5697,13 +5697,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.266154781037003</v>
+        <v>0.266190035845951</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2179814945462883</v>
+        <v>0.2136221263017037</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2742873336770451</v>
+        <v>0.2730155076701218</v>
       </c>
       <c r="K4" s="4">
         <v>70.41609977324256</v>
@@ -5729,13 +5729,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>90</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="C5" s="3">
         <v>3.333333333333333</v>
       </c>
       <c r="D5" s="3">
-        <v>6.666666666666667</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -5744,16 +5744,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <v>6.666666666666667</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="H5" s="4">
-        <v>1.205755515766875</v>
+        <v>0.8135386300411482</v>
       </c>
       <c r="I5" s="4">
-        <v>0.658061639306006</v>
+        <v>0.2256126001986039</v>
       </c>
       <c r="J5" s="4">
-        <v>1.602590063902916</v>
+        <v>1.217559863260491</v>
       </c>
       <c r="K5" s="4">
         <v>78.94897959183665</v>
@@ -5797,13 +5797,13 @@
         <v>3.333333333333333</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4098728289733117</v>
+        <v>0.3703949085080239</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3321806318348889</v>
+        <v>0.2820132997224172</v>
       </c>
       <c r="J6" s="4">
-        <v>0.4403944912223696</v>
+        <v>0.4065902207810723</v>
       </c>
       <c r="K6" s="4">
         <v>81.014739229025</v>
@@ -5847,13 +5847,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.8583176326679273</v>
+        <v>0.8567263298808636</v>
       </c>
       <c r="I7" s="4">
-        <v>0.08611096827320609</v>
+        <v>0.08521565374340517</v>
       </c>
       <c r="J7" s="4">
-        <v>1.914151321119695</v>
+        <v>1.911734262416818</v>
       </c>
       <c r="K7" s="4">
         <v>80.54308390022695</v>
@@ -5897,13 +5897,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.5962980691725904</v>
+        <v>0.5938864721918922</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1614987170804089</v>
+        <v>0.1601670305430176</v>
       </c>
       <c r="J8" s="4">
-        <v>1.025615705787393</v>
+        <v>1.025172143229493</v>
       </c>
       <c r="K8" s="4">
         <v>77.02721088435359</v>
@@ -5947,13 +5947,13 @@
         <v>3.333333333333333</v>
       </c>
       <c r="H9" s="4">
-        <v>0.5144109121512737</v>
+        <v>0.50806755052472</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3555107187784263</v>
+        <v>0.3052644119494222</v>
       </c>
       <c r="J9" s="4">
-        <v>0.5653068064540883</v>
+        <v>0.5691845700819006</v>
       </c>
       <c r="K9" s="4">
         <v>80.9478458049887</v>
@@ -5997,13 +5997,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1463573766019841</v>
+        <v>0.1429280003751532</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1424809810087452</v>
+        <v>0.1386705629789331</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1609600690771466</v>
+        <v>0.1581379652914008</v>
       </c>
       <c r="K10" s="4">
         <v>74.48412698412719</v>
@@ -6047,13 +6047,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.8046426502261911</v>
+        <v>0.8011444873049186</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1432292623703846</v>
+        <v>0.1404711733636889</v>
       </c>
       <c r="J11" s="4">
-        <v>2.962760703093565</v>
+        <v>2.959504451510899</v>
       </c>
       <c r="K11" s="4">
         <v>77.64852607709763</v>
@@ -6097,13 +6097,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.4567077948111091</v>
+        <v>0.4483177930536233</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1723191167871636</v>
+        <v>0.1674438742047641</v>
       </c>
       <c r="J12" s="4">
-        <v>1.103732132844364</v>
+        <v>1.09270104272097</v>
       </c>
       <c r="K12" s="4">
         <v>73.77437641723354</v>
@@ -6147,13 +6147,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>1.010826338034906</v>
+        <v>1.004336016925784</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2196162152342692</v>
+        <v>0.2143231822209836</v>
       </c>
       <c r="J13" s="4">
-        <v>1.890809465341965</v>
+        <v>1.881531753346523</v>
       </c>
       <c r="K13" s="4">
         <v>80.45578231292534</v>
@@ -6197,13 +6197,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.05269758308140497</v>
+        <v>0.05191404899608928</v>
       </c>
       <c r="I14" s="4">
-        <v>0.05178053232261595</v>
+        <v>0.0509099388944874</v>
       </c>
       <c r="J14" s="4">
-        <v>0.05742654122106462</v>
+        <v>0.05688582509647168</v>
       </c>
       <c r="K14" s="4">
         <v>90.94557823129233</v>
@@ -6247,13 +6247,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.381290600898786</v>
+        <v>0.3806765564466314</v>
       </c>
       <c r="I15" s="4">
-        <v>0.3466053821394308</v>
+        <v>0.3459701637406501</v>
       </c>
       <c r="J15" s="4">
-        <v>0.4101185145143642</v>
+        <v>0.4079046167167688</v>
       </c>
       <c r="K15" s="4">
         <v>76.44104308390017</v>
@@ -6297,13 +6297,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.04855648751617473</v>
+        <v>0.04820449640816218</v>
       </c>
       <c r="I16" s="4">
-        <v>0.05009384836011983</v>
+        <v>0.04970274712899476</v>
       </c>
       <c r="J16" s="4">
-        <v>0.06132908069100877</v>
+        <v>0.06085381771420403</v>
       </c>
       <c r="K16" s="4">
         <v>90.297052154195</v>
@@ -6347,13 +6347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.5187689966075774</v>
+        <v>0.5154422135985983</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2675873830166737</v>
+        <v>0.2659001803789532</v>
       </c>
       <c r="J17" s="4">
-        <v>1.452278902391568</v>
+        <v>1.453580211575058</v>
       </c>
       <c r="K17" s="4">
         <v>73.69614512471648</v>
@@ -7324,13 +7324,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="5">
         <v>1</v>
       </c>
       <c r="D5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="5">
         <v>0</v>
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -8050,16 +8050,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3488383592858471</v>
+        <v>-0.3879955977390637</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09805841744811974</v>
+        <v>0.09089993250348595</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09805841744811974</v>
+        <v>0.09089993250348595</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -8109,16 +8109,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1554799685016203</v>
+        <v>0.175591602732311</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>1.116131417077144</v>
+        <v>1.110646425923319</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1222544071810891</v>
+        <v>0.1200197811554568</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -8462,16 +8462,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3453405355259747</v>
+        <v>-0.2886003418170731</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1549147202998773</v>
+        <v>0.1537103481482931</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.159086643292394</v>
+        <v>0.1520878145547613</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -8521,16 +8521,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4073913934531447</v>
+        <v>0.36280847326816</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1765620915692786</v>
+        <v>0.1778626131998118</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1685078675563272</v>
+        <v>0.1654801493314153</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -8870,16 +8870,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2295051564198564</v>
+        <v>-0.2633501013260684</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1111106003615029</v>
+        <v>0.09832999677052033</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1111106003615029</v>
+        <v>0.09832999677052033</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -8929,22 +8929,22 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>1.688313971091371</v>
+        <v>-0.04273473582725273</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>2.932727015593192</v>
+        <v>1.875825203568556</v>
       </c>
       <c r="Q4" s="4">
-        <v>1.564772751419264</v>
+        <v>0.2773029946572933</v>
       </c>
       <c r="R4" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -9282,16 +9282,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3600486058054561</v>
+        <v>-0.3937101632764097</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1300122654042639</v>
+        <v>0.1269521238159954</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1300122654042639</v>
+        <v>0.1269521238159954</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -9341,16 +9341,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3221082164861648</v>
+        <v>0.05159319918311667</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5643922479704532</v>
+        <v>0.4597853337443005</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3545368181687413</v>
+        <v>0.2124177107896685</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -9694,16 +9694,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2179855733083969</v>
+        <v>-0.230376269959379</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04919492506980367</v>
+        <v>0.04806849810153257</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04919492506980367</v>
+        <v>0.04806849810153257</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -9753,16 +9753,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.001144310746086477</v>
+        <v>0.01292710639972938</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>2.168674849747869</v>
+        <v>2.165461360024148</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07111884319125733</v>
+        <v>0.06980964367418589</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
